--- a/9_Documentacion/WebHablaVao/HABLAVAO_cronograma_Agil_v1.0.xlsx
+++ b/9_Documentacion/WebHablaVao/HABLAVAO_cronograma_Agil_v1.0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SOPORTE\Desktop\vaope-bi\9_Documentacion\WebHablaVao\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JOHAN\Desktop\vaope-bi\9_Documentacion\WebHablaVao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C943590-8B77-40CB-A0EE-C2087F8F86DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1FDA622-4E8B-4B0B-8E0F-3DB6DBA2E71D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="3" xr2:uid="{874EE092-DFBE-4733-8E84-3FB786537FDD}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="3" xr2:uid="{874EE092-DFBE-4733-8E84-3FB786537FDD}"/>
   </bookViews>
   <sheets>
     <sheet name="HABLAVAO_cronograma_PMBAgil" sheetId="1" state="hidden" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="Backlog" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Backlog!$A$1:$I$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Backlog!$A$4:$K$36</definedName>
     <definedName name="Hoy" localSheetId="1">TODAY()</definedName>
     <definedName name="Incremento_de_desplazamiento" localSheetId="1">Gantt!$C$7</definedName>
     <definedName name="Inicio_del_proyecto" localSheetId="1">Gantt!$C$6</definedName>
@@ -34,8 +34,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -43,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="386">
   <si>
     <t>ID</t>
   </si>
@@ -358,9 +356,6 @@
     <t>Vista de mapa con pins</t>
   </si>
   <si>
-    <t>HU5.3</t>
-  </si>
-  <si>
     <t>SEO y compartido social</t>
   </si>
   <si>
@@ -485,9 +480,6 @@
   </si>
   <si>
     <t>alimentar el parser</t>
-  </si>
-  <si>
-    <t>Parser de ficha y mapeo</t>
   </si>
   <si>
     <t>extraer campos estructurados del detalle</t>
@@ -1084,21 +1076,6 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> una URL de evento Cuando parseo el HTML/render Entonces obtengo: title, starts_at, ends_at, address, region, artists[], ticket_url, lat, lng, source_event_id, published_at, updated_at, disclaimer.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Dado</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> registros crudos Cuando normalizo Entonces fechas en ISO-8601 UTC; región ∈ catálogo; dedup por (source, source_event_id) y hash de respaldo.</t>
     </r>
   </si>
   <si>
@@ -1495,13 +1472,85 @@
     <t>2.3.8 Cierre: lecciones aprendidas + handover</t>
   </si>
   <si>
-    <t>selenium, beautifulsoap, scray</t>
-  </si>
-  <si>
     <t>OK</t>
   </si>
   <si>
     <t>EN PROCESO</t>
+  </si>
+  <si>
+    <t>(Joinnus) – Crawler de listados paginados (API preferente)</t>
+  </si>
+  <si>
+    <t>(Joinnus) – Parser de detalle</t>
+  </si>
+  <si>
+    <t>DoD: upsert canónico (event, venue, region), mapeo fechas/categorías.</t>
+  </si>
+  <si>
+    <t>url_queue con detail_url + meta_json, dedupe idempotente, logs y métricas.</t>
+  </si>
+  <si>
+    <t>(Ticketmaster) – Crawler / HU4 – Parser</t>
+  </si>
+  <si>
+    <t>(Ticketmaster) – Parser de detalle</t>
+  </si>
+  <si>
+    <t>(Vaope) – Parser de detalle</t>
+  </si>
+  <si>
+    <t>(Vaope) – Conector propio (API)</t>
+  </si>
+  <si>
+    <t>Consolidación multi-fuente</t>
+  </si>
+  <si>
+    <t>Reglas de “merge” por same_event (fuzzy por título+fecha+venue), prioridad por fuente, last_seen.</t>
+  </si>
+  <si>
+    <t>HU3.9</t>
+  </si>
+  <si>
+    <t>HU4.3</t>
+  </si>
+  <si>
+    <t>HU4.4</t>
+  </si>
+  <si>
+    <t>HU4.5</t>
+  </si>
+  <si>
+    <t>HU4.6</t>
+  </si>
+  <si>
+    <t>HU7.1</t>
+  </si>
+  <si>
+    <t>HU7.2</t>
+  </si>
+  <si>
+    <t>HU7.3</t>
+  </si>
+  <si>
+    <t>Parser de ficha y mapeo Teleticket</t>
+  </si>
+  <si>
+    <t>HU4.7</t>
+  </si>
+  <si>
+    <t>HU4.8</t>
+  </si>
+  <si>
+    <t>selenium</t>
+  </si>
+  <si>
+    <t>(Conciertos.pe) – Conector propio (API)</t>
+  </si>
+  <si>
+    <t>(Conciertos.pe) – Parser de detalle</t>
+  </si>
+  <si>
+    <t>Dado registros crudos Cuando normalizo Entonces fechas en ISO-8601 UTC; región ∈ catálogo; dedup por (source, source_event_id) y hash de respaldo.</t>
   </si>
 </sst>
 </file>
@@ -1513,7 +1562,7 @@
     <numFmt numFmtId="165" formatCode="#,##0_ ;\-#,##0\ "/>
     <numFmt numFmtId="166" formatCode="#,##0.00_ ;\-#,##0.00\ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1705,6 +1754,20 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="46">
@@ -2235,7 +2298,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2412,31 +2475,26 @@
     <xf numFmtId="9" fontId="21" fillId="43" borderId="0" xfId="47" applyFont="1" applyFill="1" applyBorder="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="44" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="44" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="44" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="45" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="45" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="17" fontId="21" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="44" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="45" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="28" fillId="45" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="33" borderId="0" xfId="43" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -2451,6 +2509,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="21" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3802,16 +3869,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50936B00-7087-4246-B5F9-6B4817717132}">
   <dimension ref="A1:I43"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="45" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.44140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -3828,7 +3895,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>4</v>
@@ -3837,7 +3904,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I1" s="6" t="s">
         <v>6</v>
@@ -3848,7 +3915,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C2" s="7"/>
       <c r="D2" s="7"/>
@@ -3860,16 +3927,16 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C3" t="s">
         <v>174</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D3" t="s">
         <v>175</v>
-      </c>
-      <c r="C3" t="s">
-        <v>176</v>
-      </c>
-      <c r="D3" t="s">
-        <v>177</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -3878,30 +3945,30 @@
         <v>7</v>
       </c>
       <c r="H3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G4" t="s">
         <v>7</v>
@@ -3910,27 +3977,27 @@
         <v>9</v>
       </c>
       <c r="I4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B5" t="s">
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E5">
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G5" t="s">
         <v>11</v>
@@ -3939,27 +4006,27 @@
         <v>12</v>
       </c>
       <c r="I5" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
+        <v>182</v>
+      </c>
+      <c r="B6" t="s">
+        <v>183</v>
+      </c>
+      <c r="C6" t="s">
+        <v>181</v>
+      </c>
+      <c r="D6" t="s">
         <v>184</v>
-      </c>
-      <c r="B6" t="s">
-        <v>185</v>
-      </c>
-      <c r="C6" t="s">
-        <v>183</v>
-      </c>
-      <c r="D6" t="s">
-        <v>186</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G6" t="s">
         <v>7</v>
@@ -3968,27 +4035,27 @@
         <v>13</v>
       </c>
       <c r="I6" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D7" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G7" t="s">
         <v>7</v>
@@ -3997,27 +4064,27 @@
         <v>15</v>
       </c>
       <c r="I7" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B8" t="s">
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D8" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E8">
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G8" t="s">
         <v>7</v>
@@ -4026,27 +4093,27 @@
         <v>17</v>
       </c>
       <c r="I8" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B9" t="s">
         <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G9" t="s">
         <v>7</v>
@@ -4055,27 +4122,27 @@
         <v>19</v>
       </c>
       <c r="I9" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B10" t="s">
         <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D10" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E10">
         <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G10" t="s">
         <v>7</v>
@@ -4084,27 +4151,27 @@
         <v>21</v>
       </c>
       <c r="I10" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B11" t="s">
         <v>22</v>
       </c>
       <c r="C11" t="s">
+        <v>179</v>
+      </c>
+      <c r="D11" t="s">
         <v>181</v>
-      </c>
-      <c r="D11" t="s">
-        <v>183</v>
       </c>
       <c r="E11">
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G11" t="s">
         <v>7</v>
@@ -4113,27 +4180,27 @@
         <v>23</v>
       </c>
       <c r="I11" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B12" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C12" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D12" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E12">
         <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G12" t="s">
         <v>11</v>
@@ -4142,27 +4209,27 @@
         <v>12</v>
       </c>
       <c r="I12" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B13" t="s">
         <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D13" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G13" t="s">
         <v>11</v>
@@ -4171,27 +4238,27 @@
         <v>17</v>
       </c>
       <c r="I13" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B14" t="s">
         <v>25</v>
       </c>
       <c r="C14" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D14" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G14" t="s">
         <v>26</v>
@@ -4200,7 +4267,7 @@
         <v>19</v>
       </c>
       <c r="I14" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -4213,22 +4280,22 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B16" t="s">
         <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D16" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E16">
         <v>3</v>
       </c>
       <c r="F16" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="G16" t="s">
         <v>26</v>
@@ -4242,22 +4309,22 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B17" t="s">
         <v>28</v>
       </c>
       <c r="C17" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D17" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E17">
         <v>2</v>
       </c>
       <c r="F17" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G17" t="s">
         <v>7</v>
@@ -4271,22 +4338,22 @@
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B18" t="s">
         <v>30</v>
       </c>
       <c r="C18" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D18" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E18">
         <v>2</v>
       </c>
       <c r="F18" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G18" t="s">
         <v>26</v>
@@ -4300,22 +4367,22 @@
     </row>
     <row r="19" spans="1:9">
       <c r="A19" t="s">
+        <v>202</v>
+      </c>
+      <c r="B19" t="s">
+        <v>203</v>
+      </c>
+      <c r="C19" t="s">
+        <v>200</v>
+      </c>
+      <c r="D19" t="s">
         <v>204</v>
-      </c>
-      <c r="B19" t="s">
-        <v>205</v>
-      </c>
-      <c r="C19" t="s">
-        <v>202</v>
-      </c>
-      <c r="D19" t="s">
-        <v>206</v>
       </c>
       <c r="E19">
         <v>2</v>
       </c>
       <c r="F19" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G19" t="s">
         <v>26</v>
@@ -4329,22 +4396,22 @@
     </row>
     <row r="20" spans="1:9">
       <c r="A20" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B20" t="s">
         <v>31</v>
       </c>
       <c r="C20" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D20" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E20">
         <v>1</v>
       </c>
       <c r="F20" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="G20" t="s">
         <v>7</v>
@@ -4358,22 +4425,22 @@
     </row>
     <row r="21" spans="1:9">
       <c r="A21" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B21" t="s">
         <v>32</v>
       </c>
       <c r="C21" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D21" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E21">
         <v>1</v>
       </c>
       <c r="F21" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G21" t="s">
         <v>11</v>
@@ -4395,22 +4462,22 @@
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
+        <v>210</v>
+      </c>
+      <c r="B23" t="s">
+        <v>211</v>
+      </c>
+      <c r="C23" t="s">
+        <v>208</v>
+      </c>
+      <c r="D23" t="s">
         <v>212</v>
-      </c>
-      <c r="B23" t="s">
-        <v>213</v>
-      </c>
-      <c r="C23" t="s">
-        <v>210</v>
-      </c>
-      <c r="D23" t="s">
-        <v>214</v>
       </c>
       <c r="E23">
         <v>4</v>
       </c>
       <c r="F23" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G23" t="s">
         <v>26</v>
@@ -4424,22 +4491,22 @@
     </row>
     <row r="24" spans="1:9">
       <c r="A24" t="s">
+        <v>213</v>
+      </c>
+      <c r="B24" t="s">
+        <v>214</v>
+      </c>
+      <c r="C24" t="s">
+        <v>212</v>
+      </c>
+      <c r="D24" t="s">
         <v>215</v>
-      </c>
-      <c r="B24" t="s">
-        <v>216</v>
-      </c>
-      <c r="C24" t="s">
-        <v>214</v>
-      </c>
-      <c r="D24" t="s">
-        <v>217</v>
       </c>
       <c r="E24">
         <v>2</v>
       </c>
       <c r="F24" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="G24" t="s">
         <v>26</v>
@@ -4453,22 +4520,22 @@
     </row>
     <row r="25" spans="1:9">
       <c r="A25" t="s">
+        <v>216</v>
+      </c>
+      <c r="B25" t="s">
+        <v>217</v>
+      </c>
+      <c r="C25" t="s">
+        <v>212</v>
+      </c>
+      <c r="D25" t="s">
         <v>218</v>
-      </c>
-      <c r="B25" t="s">
-        <v>219</v>
-      </c>
-      <c r="C25" t="s">
-        <v>214</v>
-      </c>
-      <c r="D25" t="s">
-        <v>220</v>
       </c>
       <c r="E25">
         <v>3</v>
       </c>
       <c r="F25" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="G25" t="s">
         <v>11</v>
@@ -4482,22 +4549,22 @@
     </row>
     <row r="26" spans="1:9">
       <c r="A26" t="s">
+        <v>219</v>
+      </c>
+      <c r="B26" t="s">
+        <v>220</v>
+      </c>
+      <c r="C26" t="s">
+        <v>218</v>
+      </c>
+      <c r="D26" t="s">
         <v>221</v>
-      </c>
-      <c r="B26" t="s">
-        <v>222</v>
-      </c>
-      <c r="C26" t="s">
-        <v>220</v>
-      </c>
-      <c r="D26" t="s">
-        <v>223</v>
       </c>
       <c r="E26">
         <v>3</v>
       </c>
       <c r="F26" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="G26" t="s">
         <v>26</v>
@@ -4511,22 +4578,22 @@
     </row>
     <row r="27" spans="1:9">
       <c r="A27" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B27" t="s">
         <v>34</v>
       </c>
       <c r="C27" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D27" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E27">
         <v>3</v>
       </c>
       <c r="F27" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G27" t="s">
         <v>26</v>
@@ -4540,22 +4607,22 @@
     </row>
     <row r="28" spans="1:9">
       <c r="A28" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B28" t="s">
         <v>35</v>
       </c>
       <c r="C28" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D28" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E28">
         <v>2</v>
       </c>
       <c r="F28" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="G28" t="s">
         <v>26</v>
@@ -4569,22 +4636,22 @@
     </row>
     <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B29" t="s">
         <v>36</v>
       </c>
       <c r="C29" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D29" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E29">
         <v>2</v>
       </c>
       <c r="F29" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G29" t="s">
         <v>7</v>
@@ -4598,22 +4665,22 @@
     </row>
     <row r="30" spans="1:9">
       <c r="A30" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B30" t="s">
         <v>37</v>
       </c>
       <c r="C30" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D30" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E30">
         <v>1</v>
       </c>
       <c r="F30" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="G30" t="s">
         <v>11</v>
@@ -4635,22 +4702,22 @@
     </row>
     <row r="32" spans="1:9">
       <c r="A32" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B32" t="s">
         <v>38</v>
       </c>
       <c r="C32" t="s">
+        <v>231</v>
+      </c>
+      <c r="D32" t="s">
         <v>233</v>
-      </c>
-      <c r="D32" t="s">
-        <v>235</v>
       </c>
       <c r="E32">
         <v>5</v>
       </c>
       <c r="F32" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="G32" t="s">
         <v>26</v>
@@ -4664,22 +4731,22 @@
     </row>
     <row r="33" spans="1:9">
       <c r="A33" t="s">
+        <v>234</v>
+      </c>
+      <c r="B33" t="s">
+        <v>235</v>
+      </c>
+      <c r="C33" t="s">
+        <v>231</v>
+      </c>
+      <c r="D33" t="s">
         <v>236</v>
-      </c>
-      <c r="B33" t="s">
-        <v>237</v>
-      </c>
-      <c r="C33" t="s">
-        <v>233</v>
-      </c>
-      <c r="D33" t="s">
-        <v>238</v>
       </c>
       <c r="E33">
         <v>2</v>
       </c>
       <c r="F33" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="G33" t="s">
         <v>26</v>
@@ -4693,22 +4760,22 @@
     </row>
     <row r="34" spans="1:9">
       <c r="A34" t="s">
+        <v>237</v>
+      </c>
+      <c r="B34" t="s">
+        <v>238</v>
+      </c>
+      <c r="C34" t="s">
+        <v>233</v>
+      </c>
+      <c r="D34" t="s">
         <v>239</v>
-      </c>
-      <c r="B34" t="s">
-        <v>240</v>
-      </c>
-      <c r="C34" t="s">
-        <v>235</v>
-      </c>
-      <c r="D34" t="s">
-        <v>241</v>
       </c>
       <c r="E34">
         <v>2</v>
       </c>
       <c r="F34" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="G34" t="s">
         <v>26</v>
@@ -4722,22 +4789,22 @@
     </row>
     <row r="35" spans="1:9">
       <c r="A35" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B35" t="s">
         <v>40</v>
       </c>
       <c r="C35" t="s">
+        <v>239</v>
+      </c>
+      <c r="D35" t="s">
         <v>241</v>
-      </c>
-      <c r="D35" t="s">
-        <v>243</v>
       </c>
       <c r="E35">
         <v>2</v>
       </c>
       <c r="F35" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="G35" t="s">
         <v>11</v>
@@ -4751,22 +4818,22 @@
     </row>
     <row r="36" spans="1:9">
       <c r="A36" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B36" t="s">
         <v>41</v>
       </c>
       <c r="C36" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D36" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E36">
         <v>3</v>
       </c>
       <c r="F36" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="G36" t="s">
         <v>26</v>
@@ -4780,22 +4847,22 @@
     </row>
     <row r="37" spans="1:9">
       <c r="A37" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B37" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C37" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D37" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E37">
         <v>2</v>
       </c>
       <c r="F37" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="G37" t="s">
         <v>7</v>
@@ -4809,22 +4876,22 @@
     </row>
     <row r="38" spans="1:9">
       <c r="A38" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B38" t="s">
         <v>42</v>
       </c>
       <c r="C38" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D38" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E38">
         <v>2</v>
       </c>
       <c r="F38" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="G38" t="s">
         <v>11</v>
@@ -4838,28 +4905,28 @@
     </row>
     <row r="39" spans="1:9">
       <c r="A39" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B39" t="s">
         <v>43</v>
       </c>
       <c r="C39" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D39" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E39">
         <v>1</v>
       </c>
       <c r="F39" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G39" t="s">
         <v>7</v>
       </c>
       <c r="H39" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I39" t="s">
         <v>39</v>
@@ -4873,25 +4940,25 @@
         <v>45</v>
       </c>
       <c r="C40" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D40" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E40">
         <v>0</v>
       </c>
       <c r="F40" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G40" t="s">
         <v>7</v>
       </c>
       <c r="H40" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I40" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -4902,22 +4969,22 @@
         <v>47</v>
       </c>
       <c r="C41" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D41" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E41">
         <v>0</v>
       </c>
       <c r="F41" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G41" t="s">
         <v>11</v>
       </c>
       <c r="H41" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I41" t="s">
         <v>29</v>
@@ -4931,22 +4998,22 @@
         <v>49</v>
       </c>
       <c r="C42" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D42" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E42">
         <v>0</v>
       </c>
       <c r="F42" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="G42" t="s">
         <v>11</v>
       </c>
       <c r="H42" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I42" t="s">
         <v>33</v>
@@ -4960,22 +5027,22 @@
         <v>51</v>
       </c>
       <c r="C43" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D43" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E43">
         <v>0</v>
       </c>
       <c r="F43" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G43" t="s">
         <v>11</v>
       </c>
       <c r="H43" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I43" t="s">
         <v>39</v>
@@ -4992,57 +5059,57 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:KX49"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="4.7109375" style="34" customWidth="1"/>
-    <col min="2" max="2" width="83.85546875" style="10" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" style="10" customWidth="1"/>
-    <col min="4" max="4" width="36.5703125" style="10" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.42578125" style="59" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" style="59" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.42578125" style="10" customWidth="1"/>
-    <col min="9" max="9" width="1.140625" style="10" customWidth="1"/>
-    <col min="10" max="313" width="3.5703125" style="10" customWidth="1"/>
-    <col min="314" max="314" width="7.85546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="315" max="341" width="3.5703125" style="10" customWidth="1"/>
-    <col min="342" max="342" width="7.42578125" style="10" bestFit="1" customWidth="1"/>
-    <col min="343" max="402" width="3.5703125" style="10" customWidth="1"/>
-    <col min="403" max="403" width="7.7109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="404" max="432" width="3.5703125" style="10" customWidth="1"/>
-    <col min="433" max="433" width="7.140625" style="10" bestFit="1" customWidth="1"/>
-    <col min="434" max="463" width="3.5703125" style="10" customWidth="1"/>
-    <col min="464" max="464" width="7.7109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="465" max="494" width="3.5703125" style="10" customWidth="1"/>
-    <col min="495" max="495" width="7.140625" style="10" bestFit="1" customWidth="1"/>
-    <col min="496" max="524" width="3.5703125" style="10" customWidth="1"/>
-    <col min="525" max="16384" width="9.140625" style="10"/>
+    <col min="1" max="1" width="4.6640625" style="34" customWidth="1"/>
+    <col min="2" max="2" width="83.88671875" style="10" customWidth="1"/>
+    <col min="3" max="3" width="20.88671875" style="10" customWidth="1"/>
+    <col min="4" max="4" width="36.5546875" style="10" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.44140625" style="59" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.88671875" style="59" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.44140625" style="10" customWidth="1"/>
+    <col min="9" max="9" width="1.109375" style="10" customWidth="1"/>
+    <col min="10" max="313" width="3.5546875" style="10" customWidth="1"/>
+    <col min="314" max="314" width="7.88671875" style="10" bestFit="1" customWidth="1"/>
+    <col min="315" max="341" width="3.5546875" style="10" customWidth="1"/>
+    <col min="342" max="342" width="7.44140625" style="10" bestFit="1" customWidth="1"/>
+    <col min="343" max="402" width="3.5546875" style="10" customWidth="1"/>
+    <col min="403" max="403" width="7.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="404" max="432" width="3.5546875" style="10" customWidth="1"/>
+    <col min="433" max="433" width="7.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="434" max="463" width="3.5546875" style="10" customWidth="1"/>
+    <col min="464" max="464" width="7.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="465" max="494" width="3.5546875" style="10" customWidth="1"/>
+    <col min="495" max="495" width="7.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="496" max="524" width="3.5546875" style="10" customWidth="1"/>
+    <col min="525" max="16384" width="9.109375" style="10"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:310" ht="25.5" customHeight="1">
       <c r="A2" s="8"/>
-      <c r="B2" s="71" t="s">
-        <v>319</v>
-      </c>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="71"/>
-      <c r="J2" s="72"/>
-      <c r="K2" s="72"/>
-      <c r="L2" s="72"/>
-      <c r="M2" s="72"/>
-      <c r="N2" s="72"/>
-      <c r="O2" s="72"/>
-      <c r="P2" s="72"/>
-      <c r="Q2" s="72"/>
-      <c r="R2" s="72"/>
-      <c r="S2" s="72"/>
-      <c r="T2" s="72"/>
-      <c r="U2" s="72"/>
+      <c r="B2" s="70" t="s">
+        <v>316</v>
+      </c>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="70"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
+      <c r="L2" s="71"/>
+      <c r="M2" s="71"/>
+      <c r="N2" s="71"/>
+      <c r="O2" s="71"/>
+      <c r="P2" s="71"/>
+      <c r="Q2" s="71"/>
+      <c r="R2" s="71"/>
+      <c r="S2" s="71"/>
+      <c r="T2" s="71"/>
+      <c r="U2" s="71"/>
       <c r="V2" s="9"/>
       <c r="W2" s="9"/>
       <c r="X2" s="9"/>
@@ -5091,7 +5158,7 @@
     <row r="3" spans="1:310" ht="14.25" customHeight="1">
       <c r="A3" s="8"/>
       <c r="B3" s="11" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C3" s="12"/>
       <c r="D3" s="13"/>
@@ -5108,57 +5175,57 @@
     <row r="4" spans="1:310">
       <c r="A4" s="8"/>
       <c r="B4" s="16" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D4" s="18"/>
       <c r="E4" s="19"/>
       <c r="F4" s="20"/>
       <c r="G4" s="20"/>
       <c r="H4" s="21" t="s">
+        <v>299</v>
+      </c>
+      <c r="I4" s="19"/>
+      <c r="J4" s="72" t="s">
+        <v>300</v>
+      </c>
+      <c r="K4" s="72"/>
+      <c r="L4" s="72"/>
+      <c r="M4" s="72"/>
+      <c r="O4" s="73" t="s">
+        <v>301</v>
+      </c>
+      <c r="P4" s="73"/>
+      <c r="Q4" s="73"/>
+      <c r="R4" s="73"/>
+      <c r="T4" s="74" t="s">
         <v>302</v>
       </c>
-      <c r="I4" s="19"/>
-      <c r="J4" s="73" t="s">
+      <c r="U4" s="74"/>
+      <c r="V4" s="74"/>
+      <c r="W4" s="74"/>
+      <c r="Y4" s="76" t="s">
         <v>303</v>
       </c>
-      <c r="K4" s="73"/>
-      <c r="L4" s="73"/>
-      <c r="M4" s="73"/>
-      <c r="O4" s="74" t="s">
+      <c r="Z4" s="76"/>
+      <c r="AA4" s="76"/>
+      <c r="AB4" s="76"/>
+      <c r="AD4" s="77" t="s">
         <v>304</v>
       </c>
-      <c r="P4" s="74"/>
-      <c r="Q4" s="74"/>
-      <c r="R4" s="74"/>
-      <c r="T4" s="75" t="s">
-        <v>305</v>
-      </c>
-      <c r="U4" s="75"/>
-      <c r="V4" s="75"/>
-      <c r="W4" s="75"/>
-      <c r="Y4" s="69" t="s">
-        <v>306</v>
-      </c>
-      <c r="Z4" s="69"/>
-      <c r="AA4" s="69"/>
-      <c r="AB4" s="69"/>
-      <c r="AD4" s="70" t="s">
-        <v>307</v>
-      </c>
-      <c r="AE4" s="70"/>
-      <c r="AF4" s="70"/>
-      <c r="AG4" s="70"/>
+      <c r="AE4" s="77"/>
+      <c r="AF4" s="77"/>
+      <c r="AG4" s="77"/>
     </row>
     <row r="5" spans="1:310">
       <c r="A5" s="8"/>
       <c r="B5" s="22" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="D5" s="18"/>
       <c r="E5" s="19"/>
@@ -5170,7 +5237,7 @@
     <row r="6" spans="1:310">
       <c r="A6" s="8"/>
       <c r="B6" s="23" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C6" s="24">
         <v>45971</v>
@@ -5181,332 +5248,332 @@
       <c r="G6" s="20"/>
       <c r="H6" s="19"/>
       <c r="I6" s="19"/>
-      <c r="J6" s="68">
+      <c r="J6" s="75">
         <v>45717</v>
       </c>
-      <c r="K6" s="68"/>
-      <c r="L6" s="68"/>
-      <c r="M6" s="68"/>
-      <c r="N6" s="68"/>
-      <c r="O6" s="68"/>
-      <c r="P6" s="68"/>
-      <c r="Q6" s="68"/>
-      <c r="R6" s="68"/>
-      <c r="S6" s="68"/>
-      <c r="T6" s="68"/>
-      <c r="U6" s="68"/>
-      <c r="V6" s="68"/>
-      <c r="W6" s="68"/>
-      <c r="X6" s="68"/>
-      <c r="Y6" s="68"/>
-      <c r="Z6" s="68"/>
-      <c r="AA6" s="68"/>
-      <c r="AB6" s="68"/>
-      <c r="AC6" s="68"/>
-      <c r="AD6" s="68"/>
-      <c r="AE6" s="68"/>
-      <c r="AF6" s="68"/>
-      <c r="AG6" s="68"/>
-      <c r="AH6" s="68"/>
-      <c r="AI6" s="68"/>
-      <c r="AJ6" s="68"/>
-      <c r="AK6" s="68"/>
-      <c r="AL6" s="68"/>
-      <c r="AM6" s="68"/>
-      <c r="AN6" s="68"/>
-      <c r="AO6" s="68">
+      <c r="K6" s="75"/>
+      <c r="L6" s="75"/>
+      <c r="M6" s="75"/>
+      <c r="N6" s="75"/>
+      <c r="O6" s="75"/>
+      <c r="P6" s="75"/>
+      <c r="Q6" s="75"/>
+      <c r="R6" s="75"/>
+      <c r="S6" s="75"/>
+      <c r="T6" s="75"/>
+      <c r="U6" s="75"/>
+      <c r="V6" s="75"/>
+      <c r="W6" s="75"/>
+      <c r="X6" s="75"/>
+      <c r="Y6" s="75"/>
+      <c r="Z6" s="75"/>
+      <c r="AA6" s="75"/>
+      <c r="AB6" s="75"/>
+      <c r="AC6" s="75"/>
+      <c r="AD6" s="75"/>
+      <c r="AE6" s="75"/>
+      <c r="AF6" s="75"/>
+      <c r="AG6" s="75"/>
+      <c r="AH6" s="75"/>
+      <c r="AI6" s="75"/>
+      <c r="AJ6" s="75"/>
+      <c r="AK6" s="75"/>
+      <c r="AL6" s="75"/>
+      <c r="AM6" s="75"/>
+      <c r="AN6" s="75"/>
+      <c r="AO6" s="75">
         <v>45748</v>
       </c>
-      <c r="AP6" s="68"/>
-      <c r="AQ6" s="68"/>
-      <c r="AR6" s="68"/>
-      <c r="AS6" s="68"/>
-      <c r="AT6" s="68"/>
-      <c r="AU6" s="68"/>
-      <c r="AV6" s="68"/>
-      <c r="AW6" s="68"/>
-      <c r="AX6" s="68"/>
-      <c r="AY6" s="68"/>
-      <c r="AZ6" s="68"/>
-      <c r="BA6" s="68"/>
-      <c r="BB6" s="68"/>
-      <c r="BC6" s="68"/>
-      <c r="BD6" s="68"/>
-      <c r="BE6" s="68"/>
-      <c r="BF6" s="68"/>
-      <c r="BG6" s="68"/>
-      <c r="BH6" s="68"/>
-      <c r="BI6" s="68"/>
-      <c r="BJ6" s="68"/>
-      <c r="BK6" s="68"/>
-      <c r="BL6" s="68"/>
-      <c r="BM6" s="68"/>
-      <c r="BN6" s="68"/>
-      <c r="BO6" s="68"/>
-      <c r="BP6" s="68"/>
-      <c r="BQ6" s="68"/>
-      <c r="BR6" s="68"/>
-      <c r="BS6" s="68">
+      <c r="AP6" s="75"/>
+      <c r="AQ6" s="75"/>
+      <c r="AR6" s="75"/>
+      <c r="AS6" s="75"/>
+      <c r="AT6" s="75"/>
+      <c r="AU6" s="75"/>
+      <c r="AV6" s="75"/>
+      <c r="AW6" s="75"/>
+      <c r="AX6" s="75"/>
+      <c r="AY6" s="75"/>
+      <c r="AZ6" s="75"/>
+      <c r="BA6" s="75"/>
+      <c r="BB6" s="75"/>
+      <c r="BC6" s="75"/>
+      <c r="BD6" s="75"/>
+      <c r="BE6" s="75"/>
+      <c r="BF6" s="75"/>
+      <c r="BG6" s="75"/>
+      <c r="BH6" s="75"/>
+      <c r="BI6" s="75"/>
+      <c r="BJ6" s="75"/>
+      <c r="BK6" s="75"/>
+      <c r="BL6" s="75"/>
+      <c r="BM6" s="75"/>
+      <c r="BN6" s="75"/>
+      <c r="BO6" s="75"/>
+      <c r="BP6" s="75"/>
+      <c r="BQ6" s="75"/>
+      <c r="BR6" s="75"/>
+      <c r="BS6" s="75">
         <v>45778</v>
       </c>
-      <c r="BT6" s="68"/>
-      <c r="BU6" s="68"/>
-      <c r="BV6" s="68"/>
-      <c r="BW6" s="68"/>
-      <c r="BX6" s="68"/>
-      <c r="BY6" s="68"/>
-      <c r="BZ6" s="68"/>
-      <c r="CA6" s="68"/>
-      <c r="CB6" s="68"/>
-      <c r="CC6" s="68"/>
-      <c r="CD6" s="68"/>
-      <c r="CE6" s="68"/>
-      <c r="CF6" s="68"/>
-      <c r="CG6" s="68"/>
-      <c r="CH6" s="68"/>
-      <c r="CI6" s="68"/>
-      <c r="CJ6" s="68"/>
-      <c r="CK6" s="68"/>
-      <c r="CL6" s="68"/>
-      <c r="CM6" s="68"/>
-      <c r="CN6" s="68"/>
-      <c r="CO6" s="68"/>
-      <c r="CP6" s="68"/>
-      <c r="CQ6" s="68"/>
-      <c r="CR6" s="68"/>
-      <c r="CS6" s="68"/>
-      <c r="CT6" s="68"/>
-      <c r="CU6" s="68"/>
-      <c r="CV6" s="68"/>
-      <c r="CW6" s="68"/>
-      <c r="CX6" s="68">
+      <c r="BT6" s="75"/>
+      <c r="BU6" s="75"/>
+      <c r="BV6" s="75"/>
+      <c r="BW6" s="75"/>
+      <c r="BX6" s="75"/>
+      <c r="BY6" s="75"/>
+      <c r="BZ6" s="75"/>
+      <c r="CA6" s="75"/>
+      <c r="CB6" s="75"/>
+      <c r="CC6" s="75"/>
+      <c r="CD6" s="75"/>
+      <c r="CE6" s="75"/>
+      <c r="CF6" s="75"/>
+      <c r="CG6" s="75"/>
+      <c r="CH6" s="75"/>
+      <c r="CI6" s="75"/>
+      <c r="CJ6" s="75"/>
+      <c r="CK6" s="75"/>
+      <c r="CL6" s="75"/>
+      <c r="CM6" s="75"/>
+      <c r="CN6" s="75"/>
+      <c r="CO6" s="75"/>
+      <c r="CP6" s="75"/>
+      <c r="CQ6" s="75"/>
+      <c r="CR6" s="75"/>
+      <c r="CS6" s="75"/>
+      <c r="CT6" s="75"/>
+      <c r="CU6" s="75"/>
+      <c r="CV6" s="75"/>
+      <c r="CW6" s="75"/>
+      <c r="CX6" s="75">
         <v>45809</v>
       </c>
-      <c r="CY6" s="68"/>
-      <c r="CZ6" s="68"/>
-      <c r="DA6" s="68"/>
-      <c r="DB6" s="68"/>
-      <c r="DC6" s="68"/>
-      <c r="DD6" s="68"/>
-      <c r="DE6" s="68"/>
-      <c r="DF6" s="68"/>
-      <c r="DG6" s="68"/>
-      <c r="DH6" s="68"/>
-      <c r="DI6" s="68"/>
-      <c r="DJ6" s="68"/>
-      <c r="DK6" s="68"/>
-      <c r="DL6" s="68"/>
-      <c r="DM6" s="68"/>
-      <c r="DN6" s="68"/>
-      <c r="DO6" s="68"/>
-      <c r="DP6" s="68"/>
-      <c r="DQ6" s="68"/>
-      <c r="DR6" s="68"/>
-      <c r="DS6" s="68"/>
-      <c r="DT6" s="68"/>
-      <c r="DU6" s="68"/>
-      <c r="DV6" s="68"/>
-      <c r="DW6" s="68"/>
-      <c r="DX6" s="68"/>
-      <c r="DY6" s="68"/>
-      <c r="DZ6" s="68"/>
-      <c r="EA6" s="68"/>
-      <c r="EB6" s="68">
+      <c r="CY6" s="75"/>
+      <c r="CZ6" s="75"/>
+      <c r="DA6" s="75"/>
+      <c r="DB6" s="75"/>
+      <c r="DC6" s="75"/>
+      <c r="DD6" s="75"/>
+      <c r="DE6" s="75"/>
+      <c r="DF6" s="75"/>
+      <c r="DG6" s="75"/>
+      <c r="DH6" s="75"/>
+      <c r="DI6" s="75"/>
+      <c r="DJ6" s="75"/>
+      <c r="DK6" s="75"/>
+      <c r="DL6" s="75"/>
+      <c r="DM6" s="75"/>
+      <c r="DN6" s="75"/>
+      <c r="DO6" s="75"/>
+      <c r="DP6" s="75"/>
+      <c r="DQ6" s="75"/>
+      <c r="DR6" s="75"/>
+      <c r="DS6" s="75"/>
+      <c r="DT6" s="75"/>
+      <c r="DU6" s="75"/>
+      <c r="DV6" s="75"/>
+      <c r="DW6" s="75"/>
+      <c r="DX6" s="75"/>
+      <c r="DY6" s="75"/>
+      <c r="DZ6" s="75"/>
+      <c r="EA6" s="75"/>
+      <c r="EB6" s="75">
         <v>45839</v>
       </c>
-      <c r="EC6" s="68"/>
-      <c r="ED6" s="68"/>
-      <c r="EE6" s="68"/>
-      <c r="EF6" s="68"/>
-      <c r="EG6" s="68"/>
-      <c r="EH6" s="68"/>
-      <c r="EI6" s="68"/>
-      <c r="EJ6" s="68"/>
-      <c r="EK6" s="68"/>
-      <c r="EL6" s="68"/>
-      <c r="EM6" s="68"/>
-      <c r="EN6" s="68"/>
-      <c r="EO6" s="68"/>
-      <c r="EP6" s="68"/>
-      <c r="EQ6" s="68"/>
-      <c r="ER6" s="68"/>
-      <c r="ES6" s="68"/>
-      <c r="ET6" s="68"/>
-      <c r="EU6" s="68"/>
-      <c r="EV6" s="68"/>
-      <c r="EW6" s="68"/>
-      <c r="EX6" s="68"/>
-      <c r="EY6" s="68"/>
-      <c r="EZ6" s="68"/>
-      <c r="FA6" s="68"/>
-      <c r="FB6" s="68"/>
-      <c r="FC6" s="68"/>
-      <c r="FD6" s="68"/>
-      <c r="FE6" s="68"/>
-      <c r="FF6" s="68"/>
-      <c r="FG6" s="68">
+      <c r="EC6" s="75"/>
+      <c r="ED6" s="75"/>
+      <c r="EE6" s="75"/>
+      <c r="EF6" s="75"/>
+      <c r="EG6" s="75"/>
+      <c r="EH6" s="75"/>
+      <c r="EI6" s="75"/>
+      <c r="EJ6" s="75"/>
+      <c r="EK6" s="75"/>
+      <c r="EL6" s="75"/>
+      <c r="EM6" s="75"/>
+      <c r="EN6" s="75"/>
+      <c r="EO6" s="75"/>
+      <c r="EP6" s="75"/>
+      <c r="EQ6" s="75"/>
+      <c r="ER6" s="75"/>
+      <c r="ES6" s="75"/>
+      <c r="ET6" s="75"/>
+      <c r="EU6" s="75"/>
+      <c r="EV6" s="75"/>
+      <c r="EW6" s="75"/>
+      <c r="EX6" s="75"/>
+      <c r="EY6" s="75"/>
+      <c r="EZ6" s="75"/>
+      <c r="FA6" s="75"/>
+      <c r="FB6" s="75"/>
+      <c r="FC6" s="75"/>
+      <c r="FD6" s="75"/>
+      <c r="FE6" s="75"/>
+      <c r="FF6" s="75"/>
+      <c r="FG6" s="75">
         <v>45870</v>
       </c>
-      <c r="FH6" s="68"/>
-      <c r="FI6" s="68"/>
-      <c r="FJ6" s="68"/>
-      <c r="FK6" s="68"/>
-      <c r="FL6" s="68"/>
-      <c r="FM6" s="68"/>
-      <c r="FN6" s="68"/>
-      <c r="FO6" s="68"/>
-      <c r="FP6" s="68"/>
-      <c r="FQ6" s="68"/>
-      <c r="FR6" s="68"/>
-      <c r="FS6" s="68"/>
-      <c r="FT6" s="68"/>
-      <c r="FU6" s="68"/>
-      <c r="FV6" s="68"/>
-      <c r="FW6" s="68"/>
-      <c r="FX6" s="68"/>
-      <c r="FY6" s="68"/>
-      <c r="FZ6" s="68"/>
-      <c r="GA6" s="68"/>
-      <c r="GB6" s="68"/>
-      <c r="GC6" s="68"/>
-      <c r="GD6" s="68"/>
-      <c r="GE6" s="68"/>
-      <c r="GF6" s="68"/>
-      <c r="GG6" s="68"/>
-      <c r="GH6" s="68"/>
-      <c r="GI6" s="68"/>
-      <c r="GJ6" s="68"/>
-      <c r="GK6" s="68"/>
-      <c r="GL6" s="68">
+      <c r="FH6" s="75"/>
+      <c r="FI6" s="75"/>
+      <c r="FJ6" s="75"/>
+      <c r="FK6" s="75"/>
+      <c r="FL6" s="75"/>
+      <c r="FM6" s="75"/>
+      <c r="FN6" s="75"/>
+      <c r="FO6" s="75"/>
+      <c r="FP6" s="75"/>
+      <c r="FQ6" s="75"/>
+      <c r="FR6" s="75"/>
+      <c r="FS6" s="75"/>
+      <c r="FT6" s="75"/>
+      <c r="FU6" s="75"/>
+      <c r="FV6" s="75"/>
+      <c r="FW6" s="75"/>
+      <c r="FX6" s="75"/>
+      <c r="FY6" s="75"/>
+      <c r="FZ6" s="75"/>
+      <c r="GA6" s="75"/>
+      <c r="GB6" s="75"/>
+      <c r="GC6" s="75"/>
+      <c r="GD6" s="75"/>
+      <c r="GE6" s="75"/>
+      <c r="GF6" s="75"/>
+      <c r="GG6" s="75"/>
+      <c r="GH6" s="75"/>
+      <c r="GI6" s="75"/>
+      <c r="GJ6" s="75"/>
+      <c r="GK6" s="75"/>
+      <c r="GL6" s="75">
         <v>45901</v>
       </c>
-      <c r="GM6" s="68"/>
-      <c r="GN6" s="68"/>
-      <c r="GO6" s="68"/>
-      <c r="GP6" s="68"/>
-      <c r="GQ6" s="68"/>
-      <c r="GR6" s="68"/>
-      <c r="GS6" s="68"/>
-      <c r="GT6" s="68"/>
-      <c r="GU6" s="68"/>
-      <c r="GV6" s="68"/>
-      <c r="GW6" s="68"/>
-      <c r="GX6" s="68"/>
-      <c r="GY6" s="68"/>
-      <c r="GZ6" s="68"/>
-      <c r="HA6" s="68"/>
-      <c r="HB6" s="68"/>
-      <c r="HC6" s="68"/>
-      <c r="HD6" s="68"/>
-      <c r="HE6" s="68"/>
-      <c r="HF6" s="68"/>
-      <c r="HG6" s="68"/>
-      <c r="HH6" s="68"/>
-      <c r="HI6" s="68"/>
-      <c r="HJ6" s="68"/>
-      <c r="HK6" s="68"/>
-      <c r="HL6" s="68">
+      <c r="GM6" s="75"/>
+      <c r="GN6" s="75"/>
+      <c r="GO6" s="75"/>
+      <c r="GP6" s="75"/>
+      <c r="GQ6" s="75"/>
+      <c r="GR6" s="75"/>
+      <c r="GS6" s="75"/>
+      <c r="GT6" s="75"/>
+      <c r="GU6" s="75"/>
+      <c r="GV6" s="75"/>
+      <c r="GW6" s="75"/>
+      <c r="GX6" s="75"/>
+      <c r="GY6" s="75"/>
+      <c r="GZ6" s="75"/>
+      <c r="HA6" s="75"/>
+      <c r="HB6" s="75"/>
+      <c r="HC6" s="75"/>
+      <c r="HD6" s="75"/>
+      <c r="HE6" s="75"/>
+      <c r="HF6" s="75"/>
+      <c r="HG6" s="75"/>
+      <c r="HH6" s="75"/>
+      <c r="HI6" s="75"/>
+      <c r="HJ6" s="75"/>
+      <c r="HK6" s="75"/>
+      <c r="HL6" s="75">
         <v>45931</v>
       </c>
-      <c r="HM6" s="68"/>
-      <c r="HN6" s="68"/>
-      <c r="HO6" s="68"/>
-      <c r="HP6" s="68"/>
-      <c r="HQ6" s="68"/>
-      <c r="HR6" s="68"/>
-      <c r="HS6" s="68"/>
-      <c r="HT6" s="68"/>
-      <c r="HU6" s="68"/>
-      <c r="HV6" s="68"/>
-      <c r="HW6" s="68"/>
-      <c r="HX6" s="68"/>
-      <c r="HY6" s="68"/>
-      <c r="HZ6" s="68"/>
-      <c r="IA6" s="68"/>
-      <c r="IB6" s="68"/>
-      <c r="IC6" s="68"/>
-      <c r="ID6" s="68"/>
-      <c r="IE6" s="68"/>
-      <c r="IF6" s="68"/>
-      <c r="IG6" s="68"/>
-      <c r="IH6" s="68"/>
-      <c r="II6" s="68"/>
-      <c r="IJ6" s="68"/>
-      <c r="IK6" s="68"/>
-      <c r="IL6" s="68"/>
-      <c r="IM6" s="68"/>
-      <c r="IN6" s="68"/>
-      <c r="IO6" s="68"/>
-      <c r="IP6" s="68"/>
-      <c r="IQ6" s="68">
+      <c r="HM6" s="75"/>
+      <c r="HN6" s="75"/>
+      <c r="HO6" s="75"/>
+      <c r="HP6" s="75"/>
+      <c r="HQ6" s="75"/>
+      <c r="HR6" s="75"/>
+      <c r="HS6" s="75"/>
+      <c r="HT6" s="75"/>
+      <c r="HU6" s="75"/>
+      <c r="HV6" s="75"/>
+      <c r="HW6" s="75"/>
+      <c r="HX6" s="75"/>
+      <c r="HY6" s="75"/>
+      <c r="HZ6" s="75"/>
+      <c r="IA6" s="75"/>
+      <c r="IB6" s="75"/>
+      <c r="IC6" s="75"/>
+      <c r="ID6" s="75"/>
+      <c r="IE6" s="75"/>
+      <c r="IF6" s="75"/>
+      <c r="IG6" s="75"/>
+      <c r="IH6" s="75"/>
+      <c r="II6" s="75"/>
+      <c r="IJ6" s="75"/>
+      <c r="IK6" s="75"/>
+      <c r="IL6" s="75"/>
+      <c r="IM6" s="75"/>
+      <c r="IN6" s="75"/>
+      <c r="IO6" s="75"/>
+      <c r="IP6" s="75"/>
+      <c r="IQ6" s="75">
         <v>45962</v>
       </c>
-      <c r="IR6" s="68"/>
-      <c r="IS6" s="68"/>
-      <c r="IT6" s="68"/>
-      <c r="IU6" s="68"/>
-      <c r="IV6" s="68"/>
-      <c r="IW6" s="68"/>
-      <c r="IX6" s="68"/>
-      <c r="IY6" s="68"/>
-      <c r="IZ6" s="68"/>
-      <c r="JA6" s="68"/>
-      <c r="JB6" s="68"/>
-      <c r="JC6" s="68"/>
-      <c r="JD6" s="68"/>
-      <c r="JE6" s="68"/>
-      <c r="JF6" s="68"/>
-      <c r="JG6" s="68"/>
-      <c r="JH6" s="68"/>
-      <c r="JI6" s="68"/>
-      <c r="JJ6" s="68"/>
-      <c r="JK6" s="68"/>
-      <c r="JL6" s="68"/>
-      <c r="JM6" s="68"/>
-      <c r="JN6" s="68"/>
-      <c r="JO6" s="68"/>
-      <c r="JP6" s="68"/>
-      <c r="JQ6" s="68"/>
-      <c r="JR6" s="68"/>
-      <c r="JS6" s="68"/>
-      <c r="JT6" s="68"/>
-      <c r="JU6" s="68"/>
-      <c r="JV6" s="68">
+      <c r="IR6" s="75"/>
+      <c r="IS6" s="75"/>
+      <c r="IT6" s="75"/>
+      <c r="IU6" s="75"/>
+      <c r="IV6" s="75"/>
+      <c r="IW6" s="75"/>
+      <c r="IX6" s="75"/>
+      <c r="IY6" s="75"/>
+      <c r="IZ6" s="75"/>
+      <c r="JA6" s="75"/>
+      <c r="JB6" s="75"/>
+      <c r="JC6" s="75"/>
+      <c r="JD6" s="75"/>
+      <c r="JE6" s="75"/>
+      <c r="JF6" s="75"/>
+      <c r="JG6" s="75"/>
+      <c r="JH6" s="75"/>
+      <c r="JI6" s="75"/>
+      <c r="JJ6" s="75"/>
+      <c r="JK6" s="75"/>
+      <c r="JL6" s="75"/>
+      <c r="JM6" s="75"/>
+      <c r="JN6" s="75"/>
+      <c r="JO6" s="75"/>
+      <c r="JP6" s="75"/>
+      <c r="JQ6" s="75"/>
+      <c r="JR6" s="75"/>
+      <c r="JS6" s="75"/>
+      <c r="JT6" s="75"/>
+      <c r="JU6" s="75"/>
+      <c r="JV6" s="75">
         <v>45992</v>
       </c>
-      <c r="JW6" s="68"/>
-      <c r="JX6" s="68"/>
-      <c r="JY6" s="68"/>
-      <c r="JZ6" s="68"/>
-      <c r="KA6" s="68"/>
-      <c r="KB6" s="68"/>
-      <c r="KC6" s="68"/>
-      <c r="KD6" s="68"/>
-      <c r="KE6" s="68"/>
-      <c r="KF6" s="68"/>
-      <c r="KG6" s="68"/>
-      <c r="KH6" s="68"/>
-      <c r="KI6" s="68"/>
-      <c r="KJ6" s="68"/>
-      <c r="KK6" s="68"/>
-      <c r="KL6" s="68"/>
-      <c r="KM6" s="68"/>
-      <c r="KN6" s="68"/>
-      <c r="KO6" s="68"/>
-      <c r="KP6" s="68"/>
-      <c r="KQ6" s="68"/>
-      <c r="KR6" s="68"/>
-      <c r="KS6" s="68"/>
-      <c r="KT6" s="68"/>
-      <c r="KU6" s="68"/>
-      <c r="KV6" s="68"/>
-      <c r="KW6" s="68"/>
-      <c r="KX6" s="68"/>
+      <c r="JW6" s="75"/>
+      <c r="JX6" s="75"/>
+      <c r="JY6" s="75"/>
+      <c r="JZ6" s="75"/>
+      <c r="KA6" s="75"/>
+      <c r="KB6" s="75"/>
+      <c r="KC6" s="75"/>
+      <c r="KD6" s="75"/>
+      <c r="KE6" s="75"/>
+      <c r="KF6" s="75"/>
+      <c r="KG6" s="75"/>
+      <c r="KH6" s="75"/>
+      <c r="KI6" s="75"/>
+      <c r="KJ6" s="75"/>
+      <c r="KK6" s="75"/>
+      <c r="KL6" s="75"/>
+      <c r="KM6" s="75"/>
+      <c r="KN6" s="75"/>
+      <c r="KO6" s="75"/>
+      <c r="KP6" s="75"/>
+      <c r="KQ6" s="75"/>
+      <c r="KR6" s="75"/>
+      <c r="KS6" s="75"/>
+      <c r="KT6" s="75"/>
+      <c r="KU6" s="75"/>
+      <c r="KV6" s="75"/>
+      <c r="KW6" s="75"/>
+      <c r="KX6" s="75"/>
     </row>
     <row r="7" spans="1:310">
       <c r="A7" s="8"/>
       <c r="B7" s="23" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C7" s="25">
         <v>1</v>
@@ -6736,16 +6803,16 @@
     <row r="9" spans="1:310">
       <c r="A9" s="8"/>
       <c r="B9" s="30" t="s">
+        <v>308</v>
+      </c>
+      <c r="C9" s="31" t="s">
+        <v>309</v>
+      </c>
+      <c r="D9" s="31" t="s">
+        <v>310</v>
+      </c>
+      <c r="E9" s="31" t="s">
         <v>311</v>
-      </c>
-      <c r="C9" s="31" t="s">
-        <v>312</v>
-      </c>
-      <c r="D9" s="31" t="s">
-        <v>313</v>
-      </c>
-      <c r="E9" s="31" t="s">
-        <v>314</v>
       </c>
       <c r="F9" s="31" t="s">
         <v>2</v>
@@ -6754,7 +6821,7 @@
         <v>3</v>
       </c>
       <c r="H9" s="31" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="I9" s="32"/>
       <c r="J9" s="33" t="str">
@@ -7964,13 +8031,13 @@
     </row>
     <row r="10" spans="1:310">
       <c r="B10" s="35" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C10" s="36" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="D10" s="37" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="E10" s="36">
         <f>+((E11*H11)+(E24*H24))/SUM(H11+H24)</f>
@@ -8103,16 +8170,16 @@
     </row>
     <row r="11" spans="1:310">
       <c r="A11" s="40" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B11" s="41" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C11" s="42" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="D11" s="43" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="E11" s="42">
         <f>+((E12*H12)+(E13*H13)+(E14*H14)+(E15*H15)+(E16*H16)+(E17*H17)+(E18*H18)+(E19*H19)+(E20*H20)+(E21*H21)+(E22*H22)+(E23*H23))/SUM(H12:H23)</f>
@@ -8245,13 +8312,13 @@
     </row>
     <row r="12" spans="1:310">
       <c r="B12" s="46" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C12" s="47" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D12" s="48" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="E12" s="49">
         <v>1</v>
@@ -8382,13 +8449,13 @@
     <row r="13" spans="1:310" s="15" customFormat="1">
       <c r="A13" s="8"/>
       <c r="B13" s="46" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C13" s="47" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D13" s="48" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="E13" s="49">
         <v>0</v>
@@ -9613,13 +9680,13 @@
     <row r="14" spans="1:310" s="15" customFormat="1">
       <c r="A14" s="8"/>
       <c r="B14" s="46" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C14" s="47" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D14" s="48" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="E14" s="49">
         <v>0.5</v>
@@ -9941,13 +10008,13 @@
     <row r="15" spans="1:310" s="15" customFormat="1">
       <c r="A15" s="8"/>
       <c r="B15" s="46" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C15" s="47" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D15" s="48" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="E15" s="49">
         <v>1</v>
@@ -10269,13 +10336,13 @@
     <row r="16" spans="1:310" s="15" customFormat="1">
       <c r="A16" s="8"/>
       <c r="B16" s="46" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C16" s="47" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D16" s="48" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="E16" s="49">
         <v>0</v>
@@ -10597,13 +10664,13 @@
     <row r="17" spans="1:310" s="15" customFormat="1">
       <c r="A17" s="8"/>
       <c r="B17" s="46" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C17" s="47" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D17" s="48" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="E17" s="49">
         <v>1</v>
@@ -10925,13 +10992,13 @@
     <row r="18" spans="1:310" s="15" customFormat="1">
       <c r="A18" s="8"/>
       <c r="B18" s="46" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C18" s="47" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D18" s="48" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="E18" s="49">
         <v>1</v>
@@ -11253,13 +11320,13 @@
     <row r="19" spans="1:310" s="15" customFormat="1">
       <c r="A19" s="8"/>
       <c r="B19" s="46" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C19" s="47" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D19" s="48" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="E19" s="49">
         <v>0</v>
@@ -11583,13 +11650,13 @@
     <row r="20" spans="1:310" s="15" customFormat="1">
       <c r="A20" s="8"/>
       <c r="B20" s="46" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C20" s="47" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D20" s="48" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="E20" s="49">
         <v>0</v>
@@ -12814,13 +12881,13 @@
     <row r="21" spans="1:310" s="15" customFormat="1">
       <c r="A21" s="8"/>
       <c r="B21" s="46" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C21" s="47" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D21" s="48" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="E21" s="49">
         <v>1</v>
@@ -13142,13 +13209,13 @@
     <row r="22" spans="1:310" s="15" customFormat="1">
       <c r="A22" s="8"/>
       <c r="B22" s="46" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C22" s="47" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D22" s="48" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="E22" s="49">
         <v>1</v>
@@ -13470,13 +13537,13 @@
     <row r="23" spans="1:310" s="15" customFormat="1">
       <c r="A23" s="8"/>
       <c r="B23" s="46" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C23" s="47" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D23" s="48" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="E23" s="49">
         <v>0</v>
@@ -13797,16 +13864,16 @@
     </row>
     <row r="24" spans="1:310" s="15" customFormat="1">
       <c r="A24" s="40" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B24" s="41" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C24" s="42" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="D24" s="43" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="E24" s="42">
         <f>+((E25*H25)+(E32*H32)+(E41*H41))/SUM(H25,H32,H41)</f>
@@ -14130,13 +14197,13 @@
     <row r="25" spans="1:310" s="15" customFormat="1">
       <c r="A25" s="8"/>
       <c r="B25" s="46" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C25" s="47" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D25" s="48" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="E25" s="60">
         <f>+((E26*H26)+(E27*H27)+(E28*H28)+(E29*H29)+(E30*H30)+(E31*H31))/SUM(H26:H31)</f>
@@ -15363,13 +15430,13 @@
     <row r="26" spans="1:310" s="15" customFormat="1">
       <c r="A26" s="8"/>
       <c r="B26" s="52" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C26" s="53" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D26" s="22" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="E26" s="54">
         <v>0.25</v>
@@ -15691,13 +15758,13 @@
     <row r="27" spans="1:310" s="15" customFormat="1">
       <c r="A27" s="8"/>
       <c r="B27" s="52" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C27" s="53" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D27" s="22" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="E27" s="54">
         <v>0.5</v>
@@ -16019,13 +16086,13 @@
     <row r="28" spans="1:310" s="15" customFormat="1">
       <c r="A28" s="8"/>
       <c r="B28" s="52" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C28" s="53" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D28" s="22" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="E28" s="54">
         <v>0</v>
@@ -16347,13 +16414,13 @@
     <row r="29" spans="1:310" s="15" customFormat="1">
       <c r="A29" s="8"/>
       <c r="B29" s="52" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C29" s="53" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D29" s="22" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="E29" s="54">
         <v>0</v>
@@ -16675,13 +16742,13 @@
     <row r="30" spans="1:310" s="15" customFormat="1">
       <c r="A30" s="8"/>
       <c r="B30" s="52" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C30" s="53" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D30" s="22" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="E30" s="54">
         <v>0</v>
@@ -17003,13 +17070,13 @@
     <row r="31" spans="1:310" s="15" customFormat="1">
       <c r="A31" s="8"/>
       <c r="B31" s="52" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C31" s="53" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D31" s="22" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="E31" s="54">
         <v>0</v>
@@ -17331,13 +17398,13 @@
     <row r="32" spans="1:310" s="15" customFormat="1">
       <c r="A32" s="8"/>
       <c r="B32" s="46" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C32" s="47" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D32" s="48" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="E32" s="60">
         <f>+((E33*H33)+(E34*H34)+(E35*H35)+(E36*H36)+(E37*H37)+(E38*H38)+(E39*H39)+(E40*H40))/SUM(H33:H40)</f>
@@ -18564,13 +18631,13 @@
     <row r="33" spans="1:310" s="15" customFormat="1">
       <c r="A33" s="8"/>
       <c r="B33" s="52" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="C33" s="53" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D33" s="22" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="E33" s="54">
         <v>0</v>
@@ -18892,13 +18959,13 @@
     <row r="34" spans="1:310" s="15" customFormat="1">
       <c r="A34" s="8"/>
       <c r="B34" s="52" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C34" s="53" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D34" s="22" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="E34" s="54">
         <v>0</v>
@@ -19220,13 +19287,13 @@
     <row r="35" spans="1:310" s="15" customFormat="1">
       <c r="A35" s="8"/>
       <c r="B35" s="52" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C35" s="53" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D35" s="22" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="E35" s="54">
         <v>0</v>
@@ -19548,13 +19615,13 @@
     <row r="36" spans="1:310" s="15" customFormat="1">
       <c r="A36" s="8"/>
       <c r="B36" s="52" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C36" s="53" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D36" s="22" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="E36" s="54">
         <v>0</v>
@@ -19876,13 +19943,13 @@
     <row r="37" spans="1:310" s="15" customFormat="1">
       <c r="A37" s="8"/>
       <c r="B37" s="52" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C37" s="53" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D37" s="22" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="E37" s="54">
         <v>0</v>
@@ -20204,13 +20271,13 @@
     <row r="38" spans="1:310" s="15" customFormat="1">
       <c r="A38" s="8"/>
       <c r="B38" s="52" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C38" s="53" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D38" s="22" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="E38" s="54">
         <v>0</v>
@@ -20532,13 +20599,13 @@
     <row r="39" spans="1:310" s="15" customFormat="1">
       <c r="A39" s="8"/>
       <c r="B39" s="52" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C39" s="53" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D39" s="22" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="E39" s="54">
         <v>0</v>
@@ -20860,13 +20927,13 @@
     <row r="40" spans="1:310" s="15" customFormat="1">
       <c r="A40" s="8"/>
       <c r="B40" s="52" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="C40" s="53" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D40" s="22" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="E40" s="54">
         <v>0</v>
@@ -21188,13 +21255,13 @@
     <row r="41" spans="1:310" s="15" customFormat="1">
       <c r="A41" s="34"/>
       <c r="B41" s="46" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C41" s="47" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D41" s="48" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="E41" s="60">
         <f>+((E42*H42)+(E43*H43)+(E44*H44)+(E45*H45)+(E46*H46)+(E47*H47)+(E48*H48)+(E49*H49))/SUM(H42:H49)</f>
@@ -22421,13 +22488,13 @@
     <row r="42" spans="1:310" s="15" customFormat="1">
       <c r="A42" s="34"/>
       <c r="B42" s="52" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C42" s="53" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D42" s="22" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="E42" s="54">
         <v>0</v>
@@ -22749,13 +22816,13 @@
     <row r="43" spans="1:310" s="15" customFormat="1">
       <c r="A43" s="34"/>
       <c r="B43" s="52" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C43" s="53" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D43" s="22" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="E43" s="54">
         <v>0</v>
@@ -23077,13 +23144,13 @@
     <row r="44" spans="1:310" s="15" customFormat="1">
       <c r="A44" s="34"/>
       <c r="B44" s="52" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C44" s="53" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D44" s="22" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="E44" s="54">
         <v>0</v>
@@ -23405,13 +23472,13 @@
     <row r="45" spans="1:310" s="15" customFormat="1">
       <c r="A45" s="34"/>
       <c r="B45" s="52" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="C45" s="53" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D45" s="22" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="E45" s="54">
         <v>0</v>
@@ -23733,13 +23800,13 @@
     <row r="46" spans="1:310" s="15" customFormat="1">
       <c r="A46" s="34"/>
       <c r="B46" s="52" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C46" s="53" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D46" s="22" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="E46" s="54">
         <v>0</v>
@@ -24061,13 +24128,13 @@
     <row r="47" spans="1:310" s="15" customFormat="1">
       <c r="A47" s="34"/>
       <c r="B47" s="52" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C47" s="53" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D47" s="22" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="E47" s="54">
         <v>0</v>
@@ -24389,13 +24456,13 @@
     <row r="48" spans="1:310" s="15" customFormat="1">
       <c r="A48" s="34"/>
       <c r="B48" s="52" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C48" s="53" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D48" s="22" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="E48" s="54">
         <v>0</v>
@@ -24717,13 +24784,13 @@
     <row r="49" spans="1:310" s="15" customFormat="1">
       <c r="A49" s="34"/>
       <c r="B49" s="52" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="C49" s="53" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D49" s="22" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="E49" s="54">
         <v>0</v>
@@ -25044,12 +25111,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="J2:O2"/>
-    <mergeCell ref="P2:U2"/>
-    <mergeCell ref="J4:M4"/>
-    <mergeCell ref="O4:R4"/>
-    <mergeCell ref="T4:W4"/>
     <mergeCell ref="JV6:KX6"/>
     <mergeCell ref="Y4:AB4"/>
     <mergeCell ref="AD4:AG4"/>
@@ -25062,6 +25123,12 @@
     <mergeCell ref="GL6:HK6"/>
     <mergeCell ref="HL6:IP6"/>
     <mergeCell ref="IQ6:JU6"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="J2:O2"/>
+    <mergeCell ref="P2:U2"/>
+    <mergeCell ref="J4:M4"/>
+    <mergeCell ref="O4:R4"/>
+    <mergeCell ref="T4:W4"/>
   </mergeCells>
   <conditionalFormatting sqref="E9:E49">
     <cfRule type="dataBar" priority="41">
@@ -25286,12 +25353,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63650051-4D63-457C-96AD-CA1E01A23817}">
   <dimension ref="B3:D9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="6.140625" customWidth="1"/>
-    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="59.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.109375" customWidth="1"/>
+    <col min="2" max="2" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="59.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:4">
@@ -25378,165 +25445,82 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{438CAE6F-474A-4899-8D88-89596FCBEB0E}">
-  <dimension ref="A1:K24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <dimension ref="A1:J36"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="25.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="118.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="118.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="30" customHeight="1">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:10">
+      <c r="A1" s="67" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="68" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="30" customHeight="1">
+      <c r="A4" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C4" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H4" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="30" customHeight="1">
+      <c r="A5" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="30" customHeight="1">
-      <c r="A2" s="62" t="s">
-        <v>133</v>
-      </c>
-      <c r="B2" s="62" t="s">
-        <v>255</v>
-      </c>
-      <c r="C2" s="63" t="s">
-        <v>256</v>
-      </c>
-      <c r="D2" s="63" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="63" t="s">
-        <v>257</v>
-      </c>
-      <c r="F2" s="63" t="s">
-        <v>258</v>
-      </c>
-      <c r="G2" s="63" t="s">
-        <v>296</v>
-      </c>
-      <c r="H2" s="63" t="s">
-        <v>71</v>
-      </c>
-      <c r="I2" s="62" t="s">
-        <v>7</v>
-      </c>
-      <c r="K2" s="64" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="30" customHeight="1">
-      <c r="A3" s="62" t="s">
-        <v>133</v>
-      </c>
-      <c r="B3" s="62" t="s">
-        <v>259</v>
-      </c>
-      <c r="C3" s="63" t="s">
-        <v>260</v>
-      </c>
-      <c r="D3" s="63" t="s">
-        <v>86</v>
-      </c>
-      <c r="E3" s="63" t="s">
-        <v>276</v>
-      </c>
-      <c r="F3" s="63" t="s">
-        <v>261</v>
-      </c>
-      <c r="G3" s="63" t="s">
-        <v>295</v>
-      </c>
-      <c r="H3" s="63" t="s">
-        <v>71</v>
-      </c>
-      <c r="I3" s="62" t="s">
-        <v>262</v>
-      </c>
-      <c r="K3" s="65" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="30" customHeight="1">
-      <c r="A4" s="4" t="s">
+      <c r="B5" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C4" s="5" t="s">
+      <c r="D5" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E5" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="F5" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="30" customHeight="1">
-      <c r="A5" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>125</v>
-      </c>
       <c r="G5" s="5" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>71</v>
@@ -25545,117 +25529,114 @@
         <v>72</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="30" customHeight="1">
+    <row r="6" spans="1:10" ht="30" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>81</v>
+        <v>112</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="30" customHeight="1">
-      <c r="A7" s="66" t="s">
-        <v>133</v>
-      </c>
-      <c r="B7" s="66" t="s">
-        <v>83</v>
-      </c>
-      <c r="C7" s="67" t="s">
-        <v>134</v>
-      </c>
-      <c r="D7" s="67" t="s">
-        <v>135</v>
-      </c>
-      <c r="E7" s="67" t="s">
-        <v>136</v>
-      </c>
-      <c r="F7" s="67" t="s">
-        <v>137</v>
-      </c>
-      <c r="G7" s="67" t="s">
-        <v>284</v>
-      </c>
-      <c r="H7" s="67" t="s">
-        <v>71</v>
-      </c>
-      <c r="I7" s="67" t="s">
+    <row r="7" spans="1:10" ht="30" customHeight="1">
+      <c r="A7" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I7" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="J7" s="61" t="s">
-        <v>362</v>
-      </c>
     </row>
-    <row r="8" spans="1:11" ht="30" customHeight="1">
-      <c r="A8" s="66" t="s">
-        <v>133</v>
-      </c>
-      <c r="B8" s="66" t="s">
-        <v>84</v>
-      </c>
-      <c r="C8" s="67" t="s">
-        <v>138</v>
-      </c>
-      <c r="D8" s="67" t="s">
-        <v>135</v>
-      </c>
-      <c r="E8" s="67" t="s">
-        <v>139</v>
-      </c>
-      <c r="F8" s="67" t="s">
-        <v>140</v>
-      </c>
-      <c r="G8" s="67" t="s">
-        <v>285</v>
-      </c>
-      <c r="H8" s="67" t="s">
-        <v>71</v>
-      </c>
-      <c r="I8" s="67" t="s">
+    <row r="8" spans="1:10" ht="30" customHeight="1">
+      <c r="A8" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I8" s="5" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="30" customHeight="1">
+    <row r="9" spans="1:10" ht="30" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>147</v>
+        <v>109</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>149</v>
+        <v>124</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>71</v>
@@ -25664,442 +25645,806 @@
         <v>72</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="30" customHeight="1">
-      <c r="A10" s="66" t="s">
-        <v>161</v>
-      </c>
-      <c r="B10" s="66" t="s">
-        <v>97</v>
-      </c>
-      <c r="C10" s="67" t="s">
-        <v>162</v>
-      </c>
-      <c r="D10" s="67" t="s">
-        <v>163</v>
-      </c>
-      <c r="E10" s="67" t="s">
-        <v>164</v>
-      </c>
-      <c r="F10" s="67" t="s">
-        <v>165</v>
-      </c>
-      <c r="G10" s="67" t="s">
-        <v>292</v>
-      </c>
-      <c r="H10" s="67" t="s">
+    <row r="10" spans="1:10" ht="30" customHeight="1">
+      <c r="A10" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="H10" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="I10" s="67" t="s">
+      <c r="I10" s="5" t="s">
         <v>72</v>
       </c>
+      <c r="J10" s="66"/>
     </row>
-    <row r="11" spans="1:11" ht="30" customHeight="1">
+    <row r="11" spans="1:10" ht="30" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>263</v>
+        <v>82</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>264</v>
+        <v>128</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>265</v>
+        <v>129</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>266</v>
+        <v>130</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>267</v>
+        <v>131</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>297</v>
+        <v>281</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="I11" s="5" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="30" customHeight="1">
-      <c r="A12" s="4" t="s">
+    <row r="12" spans="1:10" ht="30" customHeight="1">
+      <c r="A12" s="61" t="s">
+        <v>132</v>
+      </c>
+      <c r="B12" s="61" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" s="62" t="s">
         <v>133</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>86</v>
+      <c r="D12" s="62" t="s">
+        <v>134</v>
+      </c>
+      <c r="E12" s="62" t="s">
+        <v>135</v>
+      </c>
+      <c r="F12" s="62" t="s">
+        <v>136</v>
+      </c>
+      <c r="G12" s="62" t="s">
+        <v>282</v>
+      </c>
+      <c r="H12" s="62" t="s">
+        <v>71</v>
+      </c>
+      <c r="I12" s="61" t="s">
+        <v>72</v>
+      </c>
+      <c r="J12" s="65" t="s">
+        <v>382</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="30" customHeight="1">
-      <c r="A13" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>7</v>
-      </c>
+    <row r="13" spans="1:10" ht="30" customHeight="1">
+      <c r="A13" s="61" t="s">
+        <v>132</v>
+      </c>
+      <c r="B13" s="61" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="D13" s="62" t="s">
+        <v>134</v>
+      </c>
+      <c r="E13" s="62" t="s">
+        <v>137</v>
+      </c>
+      <c r="F13" s="62" t="s">
+        <v>138</v>
+      </c>
+      <c r="G13" s="62" t="s">
+        <v>283</v>
+      </c>
+      <c r="H13" s="62" t="s">
+        <v>71</v>
+      </c>
+      <c r="I13" s="61" t="s">
+        <v>72</v>
+      </c>
+      <c r="J13" s="65"/>
     </row>
-    <row r="14" spans="1:11" ht="30" customHeight="1">
-      <c r="A14" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="I14" s="5" t="s">
+    <row r="14" spans="1:10" ht="30" customHeight="1">
+      <c r="A14" s="61" t="s">
+        <v>132</v>
+      </c>
+      <c r="B14" s="61" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14" s="62" t="s">
+        <v>361</v>
+      </c>
+      <c r="D14" s="62" t="s">
+        <v>134</v>
+      </c>
+      <c r="E14" s="62" t="s">
+        <v>137</v>
+      </c>
+      <c r="F14" s="62" t="s">
+        <v>136</v>
+      </c>
+      <c r="G14" s="62" t="s">
+        <v>364</v>
+      </c>
+      <c r="H14" s="62" t="s">
+        <v>71</v>
+      </c>
+      <c r="I14" s="62" t="s">
         <v>72</v>
       </c>
+      <c r="J14" s="65"/>
     </row>
-    <row r="15" spans="1:11" ht="30" customHeight="1">
-      <c r="A15" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="I15" s="5" t="s">
+    <row r="15" spans="1:10" ht="30" customHeight="1">
+      <c r="A15" s="61" t="s">
+        <v>132</v>
+      </c>
+      <c r="B15" s="61" t="s">
+        <v>253</v>
+      </c>
+      <c r="C15" s="62" t="s">
+        <v>362</v>
+      </c>
+      <c r="D15" s="62" t="s">
+        <v>134</v>
+      </c>
+      <c r="E15" s="62" t="s">
+        <v>137</v>
+      </c>
+      <c r="F15" s="62" t="s">
+        <v>138</v>
+      </c>
+      <c r="G15" s="62" t="s">
+        <v>363</v>
+      </c>
+      <c r="H15" s="62" t="s">
+        <v>71</v>
+      </c>
+      <c r="I15" s="62" t="s">
         <v>72</v>
       </c>
+      <c r="J15" s="65"/>
     </row>
-    <row r="16" spans="1:11" ht="30" customHeight="1">
-      <c r="A16" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="I16" s="5" t="s">
+    <row r="16" spans="1:10" ht="30" customHeight="1">
+      <c r="A16" s="63" t="s">
+        <v>132</v>
+      </c>
+      <c r="B16" s="63" t="s">
+        <v>257</v>
+      </c>
+      <c r="C16" s="64" t="s">
+        <v>365</v>
+      </c>
+      <c r="D16" s="64" t="s">
+        <v>134</v>
+      </c>
+      <c r="E16" s="64" t="s">
+        <v>137</v>
+      </c>
+      <c r="F16" s="64" t="s">
+        <v>136</v>
+      </c>
+      <c r="G16" s="69" t="s">
+        <v>364</v>
+      </c>
+      <c r="H16" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="I16" s="64" t="s">
         <v>72</v>
       </c>
+      <c r="J16" s="65"/>
     </row>
-    <row r="17" spans="1:9" ht="30" customHeight="1">
+    <row r="17" spans="1:10" ht="30" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>85</v>
+        <v>261</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>141</v>
+        <v>366</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>286</v>
+        <v>363</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>86</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="J17" s="65"/>
     </row>
-    <row r="18" spans="1:9" ht="30" customHeight="1">
+    <row r="18" spans="1:10" ht="30" customHeight="1">
       <c r="A18" s="4" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>91</v>
+        <v>266</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>92</v>
+        <v>368</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>110</v>
+        <v>134</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>289</v>
+        <v>364</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I18" s="5" t="s">
         <v>72</v>
       </c>
+      <c r="J18" s="65"/>
     </row>
-    <row r="19" spans="1:9" ht="30" customHeight="1">
+    <row r="19" spans="1:10" ht="30" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>93</v>
+        <v>270</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>94</v>
+        <v>367</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>290</v>
+        <v>363</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>72</v>
       </c>
+      <c r="J19" s="65"/>
     </row>
-    <row r="20" spans="1:9" ht="30" customHeight="1">
+    <row r="20" spans="1:10" ht="30" customHeight="1">
       <c r="A20" s="4" t="s">
-        <v>161</v>
+        <v>132</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>98</v>
+        <v>371</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>99</v>
+        <v>383</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>166</v>
+        <v>134</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>167</v>
+        <v>136</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>293</v>
+        <v>364</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>7</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="J20" s="65"/>
     </row>
-    <row r="21" spans="1:9" ht="30" customHeight="1">
+    <row r="21" spans="1:10" ht="30" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>129</v>
+        <v>384</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>283</v>
+        <v>363</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="I21" s="5" t="s">
         <v>72</v>
       </c>
+      <c r="J21" s="65"/>
     </row>
-    <row r="22" spans="1:9" ht="30" customHeight="1">
-      <c r="A22" s="4" t="s">
+    <row r="22" spans="1:10" ht="30" customHeight="1">
+      <c r="A22" s="63" t="s">
+        <v>132</v>
+      </c>
+      <c r="B22" s="63" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22" s="64" t="s">
+        <v>369</v>
+      </c>
+      <c r="D22" s="64" t="s">
+        <v>134</v>
+      </c>
+      <c r="E22" s="64" t="s">
+        <v>137</v>
+      </c>
+      <c r="F22" s="64" t="s">
+        <v>138</v>
+      </c>
+      <c r="G22" s="64" t="s">
+        <v>370</v>
+      </c>
+      <c r="H22" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="I22" s="64" t="s">
+        <v>72</v>
+      </c>
+      <c r="J22" s="65"/>
+    </row>
+    <row r="23" spans="1:10" ht="30" customHeight="1">
+      <c r="A23" s="61" t="s">
+        <v>132</v>
+      </c>
+      <c r="B23" s="61" t="s">
+        <v>372</v>
+      </c>
+      <c r="C23" s="62" t="s">
+        <v>139</v>
+      </c>
+      <c r="D23" s="62" t="s">
+        <v>140</v>
+      </c>
+      <c r="E23" s="62" t="s">
+        <v>141</v>
+      </c>
+      <c r="F23" s="62" t="s">
+        <v>142</v>
+      </c>
+      <c r="G23" s="62" t="s">
+        <v>385</v>
+      </c>
+      <c r="H23" s="62" t="s">
+        <v>74</v>
+      </c>
+      <c r="I23" s="61" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="30" customHeight="1">
+      <c r="A24" s="61" t="s">
+        <v>132</v>
+      </c>
+      <c r="B24" s="61" t="s">
+        <v>373</v>
+      </c>
+      <c r="C24" s="62" t="s">
+        <v>254</v>
+      </c>
+      <c r="D24" s="62" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24" s="62" t="s">
+        <v>255</v>
+      </c>
+      <c r="F24" s="62" t="s">
+        <v>256</v>
+      </c>
+      <c r="G24" s="62" t="s">
+        <v>293</v>
+      </c>
+      <c r="H24" s="62" t="s">
+        <v>71</v>
+      </c>
+      <c r="I24" s="61" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="30" customHeight="1">
+      <c r="A25" s="61" t="s">
+        <v>132</v>
+      </c>
+      <c r="B25" s="61" t="s">
+        <v>374</v>
+      </c>
+      <c r="C25" s="62" t="s">
+        <v>258</v>
+      </c>
+      <c r="D25" s="62" t="s">
+        <v>86</v>
+      </c>
+      <c r="E25" s="62" t="s">
+        <v>274</v>
+      </c>
+      <c r="F25" s="62" t="s">
+        <v>259</v>
+      </c>
+      <c r="G25" s="62" t="s">
+        <v>292</v>
+      </c>
+      <c r="H25" s="62" t="s">
+        <v>71</v>
+      </c>
+      <c r="I25" s="61" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="30" customHeight="1">
+      <c r="A26" s="63" t="s">
+        <v>132</v>
+      </c>
+      <c r="B26" s="63" t="s">
+        <v>375</v>
+      </c>
+      <c r="C26" s="64" t="s">
+        <v>262</v>
+      </c>
+      <c r="D26" s="64" t="s">
+        <v>263</v>
+      </c>
+      <c r="E26" s="64" t="s">
+        <v>264</v>
+      </c>
+      <c r="F26" s="64" t="s">
+        <v>265</v>
+      </c>
+      <c r="G26" s="64" t="s">
+        <v>294</v>
+      </c>
+      <c r="H26" s="64" t="s">
+        <v>74</v>
+      </c>
+      <c r="I26" s="64" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="30" customHeight="1">
+      <c r="A27" s="63" t="s">
+        <v>132</v>
+      </c>
+      <c r="B27" s="63" t="s">
+        <v>380</v>
+      </c>
+      <c r="C27" s="64" t="s">
+        <v>267</v>
+      </c>
+      <c r="D27" s="64" t="s">
+        <v>86</v>
+      </c>
+      <c r="E27" s="64" t="s">
+        <v>268</v>
+      </c>
+      <c r="F27" s="64" t="s">
+        <v>269</v>
+      </c>
+      <c r="G27" s="64" t="s">
+        <v>295</v>
+      </c>
+      <c r="H27" s="64" t="s">
+        <v>74</v>
+      </c>
+      <c r="I27" s="64" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="30" customHeight="1">
+      <c r="A28" s="63" t="s">
+        <v>132</v>
+      </c>
+      <c r="B28" s="63" t="s">
+        <v>381</v>
+      </c>
+      <c r="C28" s="64" t="s">
+        <v>271</v>
+      </c>
+      <c r="D28" s="64" t="s">
+        <v>7</v>
+      </c>
+      <c r="E28" s="64" t="s">
+        <v>272</v>
+      </c>
+      <c r="F28" s="64" t="s">
+        <v>273</v>
+      </c>
+      <c r="G28" s="64" t="s">
+        <v>296</v>
+      </c>
+      <c r="H28" s="64" t="s">
+        <v>74</v>
+      </c>
+      <c r="I28" s="63" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="30" customHeight="1">
+      <c r="A29" s="63" t="s">
+        <v>143</v>
+      </c>
+      <c r="B29" s="63" t="s">
+        <v>91</v>
+      </c>
+      <c r="C29" s="64" t="s">
+        <v>144</v>
+      </c>
+      <c r="D29" s="64" t="s">
         <v>145</v>
       </c>
-      <c r="B22" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="C22" s="5" t="s">
+      <c r="E29" s="64" t="s">
+        <v>146</v>
+      </c>
+      <c r="F29" s="64" t="s">
+        <v>147</v>
+      </c>
+      <c r="G29" s="64" t="s">
+        <v>284</v>
+      </c>
+      <c r="H29" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="I29" s="64" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="30" customHeight="1">
+      <c r="A30" s="63" t="s">
+        <v>143</v>
+      </c>
+      <c r="B30" s="63" t="s">
+        <v>93</v>
+      </c>
+      <c r="C30" s="64" t="s">
         <v>89</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D30" s="64" t="s">
+        <v>148</v>
+      </c>
+      <c r="E30" s="64" t="s">
+        <v>149</v>
+      </c>
+      <c r="F30" s="64" t="s">
         <v>150</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="G30" s="64" t="s">
+        <v>285</v>
+      </c>
+      <c r="H30" s="64" t="s">
+        <v>90</v>
+      </c>
+      <c r="I30" s="64" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="30" customHeight="1">
+      <c r="A31" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="B31" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="E31" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="G22" s="5" t="s">
+      <c r="F31" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="30" customHeight="1">
+      <c r="A32" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I32" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="30" customHeight="1">
+      <c r="A33" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="G33" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="H22" s="5" t="s">
+      <c r="H33" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="I22" s="5" t="s">
+      <c r="I33" s="5" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="30" customHeight="1">
-      <c r="A23" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="D23" s="5" t="s">
+    <row r="34" spans="1:9" ht="30" customHeight="1">
+      <c r="A34" s="63" t="s">
         <v>159</v>
       </c>
-      <c r="E23" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="F23" s="5" t="s">
+      <c r="B34" s="63" t="s">
+        <v>376</v>
+      </c>
+      <c r="C34" s="64" t="s">
         <v>160</v>
       </c>
-      <c r="G23" s="5" t="s">
+      <c r="D34" s="64" t="s">
+        <v>161</v>
+      </c>
+      <c r="E34" s="64" t="s">
+        <v>162</v>
+      </c>
+      <c r="F34" s="64" t="s">
+        <v>163</v>
+      </c>
+      <c r="G34" s="64" t="s">
+        <v>289</v>
+      </c>
+      <c r="H34" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="I34" s="64" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="30" customHeight="1">
+      <c r="A35" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="30" customHeight="1">
+      <c r="A36" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="G36" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="H23" s="5" t="s">
+      <c r="H36" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="I23" s="5" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="30" customHeight="1">
-      <c r="A24" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="I24" s="4" t="s">
+      <c r="I36" s="4" t="s">
         <v>7</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="27" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
 </file>